--- a/upload/Etat d'avancement PPM 2026 au 15-05-2026.xlsx
+++ b/upload/Etat d'avancement PPM 2026 au 15-05-2026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSE 2026\Mai 2026\15-05-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11910"/>
   </bookViews>
   <sheets>
     <sheet name="Avancement PPM au 15-05-2026" sheetId="1" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="161">
   <si>
     <t>Type de budget</t>
   </si>
@@ -785,6 +785,9 @@
   </si>
   <si>
     <t>Entretien des réseaux d’irrigation y compris les stations de pompage et les réseaux d’assainissement et de drainage de l’ORMVA du Gharb au niveau des zones d’action des provinces de Kenitra, Sidi Kacem et Sidi Slimane</t>
+  </si>
+  <si>
+    <t>Nombre AO</t>
   </si>
 </sst>
 </file>
@@ -792,9 +795,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="[$-40C]d\ mmmm\ yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-40C]d\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1020,8 +1023,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1065,13 +1068,13 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1100,15 +1103,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4912,26 +4915,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
@@ -4967,13 +4970,13 @@
       <c r="Y2" s="5"/>
     </row>
     <row r="3" spans="1:25" s="6" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="30" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="33" t="s">
@@ -4998,7 +5001,7 @@
       <c r="K3" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="30" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="33" t="s">
@@ -5007,10 +5010,10 @@
       <c r="N3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="30" t="s">
         <v>13</v>
       </c>
       <c r="Q3" s="33" t="s">
@@ -5019,14 +5022,14 @@
       <c r="R3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="31" t="s">
+      <c r="S3" s="30" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:25" s="6" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="34"/>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
@@ -5039,14 +5042,14 @@
       <c r="I4" s="38"/>
       <c r="J4" s="39"/>
       <c r="K4" s="39"/>
-      <c r="L4" s="32"/>
+      <c r="L4" s="31"/>
       <c r="M4" s="34"/>
       <c r="N4" s="34"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="34"/>
-      <c r="S4" s="32"/>
+      <c r="S4" s="31"/>
     </row>
     <row r="5" spans="1:25" s="18" customFormat="1" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
@@ -6817,7 +6820,7 @@
       <c r="T37" s="6"/>
       <c r="U37" s="6"/>
     </row>
-    <row r="38" spans="1:21" s="18" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" s="18" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>34</v>
       </c>
@@ -7935,7 +7938,7 @@
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
     </row>
-    <row r="64" spans="1:21" s="18" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" s="18" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>60</v>
       </c>
@@ -8380,7 +8383,7 @@
         <v>5000</v>
       </c>
       <c r="J74" s="13">
-        <v>45965</v>
+        <v>46330</v>
       </c>
       <c r="K74" s="26" t="s">
         <v>45</v>
@@ -8421,7 +8424,7 @@
         <v>5000</v>
       </c>
       <c r="J75" s="13">
-        <v>45965</v>
+        <v>46330</v>
       </c>
       <c r="K75" s="26" t="s">
         <v>45</v>
@@ -8504,6 +8507,7 @@
     <filterColumn colId="3" showButton="0"/>
   </autoFilter>
   <mergeCells count="19">
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -8522,7 +8526,6 @@
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
